--- a/public/res/leaderboards/Advanced.xlsx
+++ b/public/res/leaderboards/Advanced.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lawrence\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lawrence\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DABC261-3C12-408C-807E-A0AFCA82090E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D808C5-D424-4055-9FBC-DF0D7C436005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{231F0BEC-F623-41AC-8721-73F4116A0546}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>#</t>
   </si>
@@ -185,10 +185,91 @@
     <t>Austin Yam</t>
   </si>
   <si>
-    <t>Itsuki Cheng</t>
-  </si>
-  <si>
     <t>Jun Chen</t>
+  </si>
+  <si>
+    <t>Zichuan Zou</t>
+  </si>
+  <si>
+    <t>Kaan Yilmaz</t>
+  </si>
+  <si>
+    <t>Keyur Gohel</t>
+  </si>
+  <si>
+    <t>finnegan clapp</t>
+  </si>
+  <si>
+    <t>Rudhra Khandelwal</t>
+  </si>
+  <si>
+    <t>avicknash dayanandan</t>
+  </si>
+  <si>
+    <t>Ty Gredina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyrus Han </t>
+  </si>
+  <si>
+    <t>Ziggy Guan</t>
+  </si>
+  <si>
+    <t>scott zhou</t>
+  </si>
+  <si>
+    <t>Andrew Nguyen</t>
+  </si>
+  <si>
+    <t>Izac Jie Ming Ooi</t>
+  </si>
+  <si>
+    <t>Jackie Xie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Rao </t>
+  </si>
+  <si>
+    <t>Jason You</t>
+  </si>
+  <si>
+    <t>Kevin Mogil</t>
+  </si>
+  <si>
+    <t>Tanvir Singh</t>
+  </si>
+  <si>
+    <t>Corey Gendala</t>
+  </si>
+  <si>
+    <t>Aashay Deo</t>
+  </si>
+  <si>
+    <t>Santiago Sassman</t>
+  </si>
+  <si>
+    <t>avnish ranchigoda</t>
+  </si>
+  <si>
+    <t>Zichen Xue</t>
+  </si>
+  <si>
+    <t>Vojtech Zeman</t>
+  </si>
+  <si>
+    <t>Zabrain Haider</t>
+  </si>
+  <si>
+    <t>Cas Chng</t>
+  </si>
+  <si>
+    <t>yi tang</t>
+  </si>
+  <si>
+    <t>kalabe araya</t>
+  </si>
+  <si>
+    <t>kevin gonzalez arias</t>
   </si>
 </sst>
 </file>
@@ -589,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97B47B5-A6D7-41E5-A619-C36FE2241088}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -626,13 +707,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>146300</v>
+        <v>71000</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>213600</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -647,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>146300</v>
+        <v>284600</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -655,13 +736,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>120000</v>
+        <v>118600</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>123300</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -676,7 +757,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>120000</v>
+        <v>241900</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -684,13 +765,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>118600</v>
+        <v>54100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>139300</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -705,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>118600</v>
+        <v>178400</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -713,13 +794,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C5">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>150700</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -734,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>118000</v>
+        <v>150700</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -742,10 +823,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>111300</v>
+        <v>146300</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -763,7 +844,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>111300</v>
+        <v>131300</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -771,13 +852,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C7">
-        <v>71900</v>
+        <v>45900</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>80700</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -792,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>71900</v>
+        <v>126600</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -800,13 +881,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C8">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>124800</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -821,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>71100</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -829,10 +910,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>71000</v>
+        <v>120000</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -850,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>71000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -858,10 +939,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>65800</v>
+        <v>118000</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -879,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>65800</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -887,13 +968,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C11">
-        <v>65600</v>
+        <v>35500</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>79200</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -908,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>65600</v>
+        <v>114700</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -916,10 +997,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>59800</v>
+        <v>111300</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -937,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>59800</v>
+        <v>111300</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -945,13 +1026,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C13">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>94500</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -966,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>58600</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -974,13 +1055,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14">
-        <v>56200</v>
+        <v>59800</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>31200</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -995,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>56200</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1003,13 +1084,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="C15">
-        <v>55500</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>88200</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1024,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>55500</v>
+        <v>88200</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1032,13 +1113,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C16">
-        <v>54600</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>84400</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1053,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>54600</v>
+        <v>84400</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1061,13 +1142,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>54100</v>
+        <v>56200</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1082,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>54100</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1090,13 +1171,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C18">
-        <v>51000</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>66400</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1111,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>51000</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1119,13 +1200,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C19">
-        <v>50400</v>
+        <v>11400</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1140,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>50400</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1148,10 +1229,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C20">
-        <v>46200</v>
+        <v>65800</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1169,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>46200</v>
+        <v>65800</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1177,10 +1258,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C21">
-        <v>45900</v>
+        <v>65600</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1198,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>45900</v>
+        <v>65600</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1206,13 +1287,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C22">
-        <v>45500</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>60900</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1227,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>45500</v>
+        <v>60900</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1235,10 +1316,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C23">
-        <v>39400</v>
+        <v>58600</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1256,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>39400</v>
+        <v>58600</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1264,13 +1345,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C24">
-        <v>37700</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>58500</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1285,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>37700</v>
+        <v>58500</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1293,10 +1374,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C25">
-        <v>35500</v>
+        <v>71900</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1314,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>35500</v>
+        <v>56900</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1322,10 +1403,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>35400</v>
+        <v>71100</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1343,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>35400</v>
+        <v>56100</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1351,10 +1432,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C27">
-        <v>34900</v>
+        <v>55500</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1372,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>34900</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1380,13 +1461,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C28">
-        <v>32100</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>53300</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1401,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>32100</v>
+        <v>53300</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1409,13 +1490,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C29">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1430,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>31200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1438,10 +1519,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C30">
-        <v>30000</v>
+        <v>51000</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1459,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>30000</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1467,10 +1548,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C31">
-        <v>29400</v>
+        <v>50400</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1488,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>29400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1496,13 +1577,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C32">
-        <v>29200</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>49800</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1517,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>29200</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1525,13 +1606,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C33">
-        <v>27300</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>49700</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1546,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>27300</v>
+        <v>49700</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1554,10 +1635,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C34">
-        <v>27200</v>
+        <v>46200</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1575,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>27200</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1583,10 +1664,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C35">
-        <v>25500</v>
+        <v>45900</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1604,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>25500</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -1612,10 +1693,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C36">
-        <v>25400</v>
+        <v>45500</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1633,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>25400</v>
+        <v>45500</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1641,13 +1722,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C37">
-        <v>21600</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>43700</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1662,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>21600</v>
+        <v>43700</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1670,13 +1751,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C38">
-        <v>18800</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1691,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>18800</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -1699,10 +1780,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C39">
-        <v>16800</v>
+        <v>54600</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1720,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>16800</v>
+        <v>39600</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -1728,10 +1809,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C40">
-        <v>13100</v>
+        <v>39400</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1749,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>13100</v>
+        <v>39400</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -1757,13 +1838,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C41">
-        <v>12400</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>39400</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1778,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>12400</v>
+        <v>39400</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1786,28 +1867,811 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>39000</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>37500</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>37500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44">
+        <v>34900</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>34900</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45">
+        <v>34400</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>34400</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46">
+        <v>27300</v>
+      </c>
+      <c r="D46">
+        <v>20500</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>32800</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47">
+        <v>32100</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>32100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>31600</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>31600</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49">
+        <v>31500</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>31500</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="C42">
+      <c r="B50" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50">
+        <v>31200</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>31200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51">
+        <v>30000</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52">
+        <v>25500</v>
+      </c>
+      <c r="D52">
+        <v>19400</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>29900</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53">
+        <v>29400</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>29400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54">
+        <v>27200</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>27200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>25400</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>25400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56">
+        <v>24000</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57">
+        <v>37700</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>22700</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>72</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>22600</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>22600</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59">
+        <v>21600</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60">
+        <v>35400</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>20400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61">
+        <v>33200</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62">
+        <v>16800</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>15600</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64">
+        <v>29200</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>14200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>47</v>
+      </c>
+      <c r="C65">
+        <v>13100</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66">
         <v>8700</v>
       </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
         <v>8700</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>3900</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68">
+        <v>18800</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>3300</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>3300</v>
       </c>
     </row>
   </sheetData>

--- a/public/res/leaderboards/Advanced.xlsx
+++ b/public/res/leaderboards/Advanced.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lawrence\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D808C5-D424-4055-9FBC-DF0D7C436005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FAE6A3-C077-48C7-BB5F-62FF1E6BE251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{231F0BEC-F623-41AC-8721-73F4116A0546}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>#</t>
   </si>
@@ -158,9 +158,6 @@
     <t>Pranay J</t>
   </si>
   <si>
-    <t>Aryamaan  Nannegari</t>
-  </si>
-  <si>
     <t>Jingxuan Sun</t>
   </si>
   <si>
@@ -245,9 +242,6 @@
     <t>Aashay Deo</t>
   </si>
   <si>
-    <t>Santiago Sassman</t>
-  </si>
-  <si>
     <t>avnish ranchigoda</t>
   </si>
   <si>
@@ -270,6 +264,54 @@
   </si>
   <si>
     <t>kevin gonzalez arias</t>
+  </si>
+  <si>
+    <t>Kevin Bao</t>
+  </si>
+  <si>
+    <t>Aryamaan Nannegari</t>
+  </si>
+  <si>
+    <t>James Deng</t>
+  </si>
+  <si>
+    <t>Toan Trinh</t>
+  </si>
+  <si>
+    <t>Jeremiah</t>
+  </si>
+  <si>
+    <t>Karwan</t>
+  </si>
+  <si>
+    <t>Yuquan  Hu</t>
+  </si>
+  <si>
+    <t>Jazim Sodha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sue Rhee </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derick </t>
+  </si>
+  <si>
+    <t>Tiger Tam</t>
+  </si>
+  <si>
+    <t>Revan Patil</t>
+  </si>
+  <si>
+    <t>Jonathan Ozernov</t>
+  </si>
+  <si>
+    <t>Keith Ng</t>
+  </si>
+  <si>
+    <t>Wilson Sha</t>
+  </si>
+  <si>
+    <t>Giorgio Atzarakis</t>
   </si>
 </sst>
 </file>
@@ -670,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97B47B5-A6D7-41E5-A619-C36FE2241088}">
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -707,16 +749,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C2">
-        <v>71000</v>
+        <v>54100</v>
       </c>
       <c r="D2">
-        <v>213600</v>
+        <v>139300</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>185300</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -728,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>284600</v>
+        <v>363700</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -736,16 +778,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>118600</v>
+        <v>71000</v>
       </c>
       <c r="D3">
-        <v>123300</v>
+        <v>213600</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -757,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>241900</v>
+        <v>349400</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -765,16 +807,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C4">
-        <v>54100</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>139300</v>
+        <v>150700</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>130800</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -786,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>178400</v>
+        <v>281500</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -794,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>118600</v>
       </c>
       <c r="D5">
-        <v>150700</v>
+        <v>123300</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -815,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>150700</v>
+        <v>226900</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -823,16 +865,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="C6">
-        <v>146300</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>225800</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -844,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>131300</v>
+        <v>225800</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -852,16 +894,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>45900</v>
+        <v>65800</v>
       </c>
       <c r="D7">
-        <v>80700</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -873,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>126600</v>
+        <v>135800</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -881,16 +923,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>29200</v>
       </c>
       <c r="D8">
-        <v>124800</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>117200</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -902,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>124800</v>
+        <v>131400</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -910,10 +952,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>120000</v>
+        <v>146300</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -931,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>120000</v>
+        <v>131300</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -939,13 +981,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C10">
-        <v>118000</v>
+        <v>45900</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>80700</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -960,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>118000</v>
+        <v>126600</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -968,13 +1010,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>35500</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>79200</v>
+        <v>124800</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -989,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>114700</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -997,16 +1039,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="C12">
-        <v>111300</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>123500</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1018,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>111300</v>
+        <v>123500</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1026,13 +1068,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="D13">
-        <v>94500</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1047,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>94500</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1055,13 +1097,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>59800</v>
+        <v>118000</v>
       </c>
       <c r="D14">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1076,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>91000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1084,13 +1126,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>35500</v>
       </c>
       <c r="D15">
-        <v>88200</v>
+        <v>79200</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1105,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>88200</v>
+        <v>114700</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1113,16 +1155,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>56200</v>
       </c>
       <c r="D16">
-        <v>84400</v>
+        <v>11400</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1134,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>84400</v>
+        <v>113600</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1142,13 +1184,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C17">
-        <v>56200</v>
+        <v>111300</v>
       </c>
       <c r="D17">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1163,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>67600</v>
+        <v>111300</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1171,16 +1213,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>66400</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>111100</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1192,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>66400</v>
+        <v>111100</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1200,16 +1242,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C19">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>55000</v>
+        <v>42000</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>61500</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1221,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>66400</v>
+        <v>103500</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1229,13 +1271,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C20">
-        <v>65800</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>94500</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1250,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>65800</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1258,16 +1300,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C21">
-        <v>65600</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>31600</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>61500</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1279,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>65600</v>
+        <v>93100</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1287,16 +1329,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>60900</v>
+        <v>37500</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>54800</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1308,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>60900</v>
+        <v>92300</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1316,16 +1358,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C23">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>82700</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1337,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>58600</v>
+        <v>82700</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1345,16 +1387,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>58500</v>
+        <v>3300</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>92700</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1366,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>58500</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1374,13 +1416,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C25">
-        <v>71900</v>
+        <v>33200</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1395,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>56900</v>
+        <v>80200</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1403,16 +1445,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C26">
-        <v>71100</v>
+        <v>11400</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1424,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>56100</v>
+        <v>77400</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1432,16 +1474,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="C27">
-        <v>55500</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>76500</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1453,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>55500</v>
+        <v>76500</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1461,13 +1503,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>59800</v>
       </c>
       <c r="D28">
-        <v>53300</v>
+        <v>31200</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1482,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>53300</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1490,13 +1532,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>52000</v>
+        <v>88200</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1511,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>52000</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1519,16 +1561,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="C30">
-        <v>51000</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>72500</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1540,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>51000</v>
+        <v>72500</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1548,13 +1590,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C31">
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>84400</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1569,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>50400</v>
+        <v>69400</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1577,16 +1619,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>49800</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>81800</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1598,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>49800</v>
+        <v>66800</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1606,13 +1648,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>49700</v>
+        <v>66400</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1627,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>49700</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1635,10 +1677,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C34">
-        <v>46200</v>
+        <v>65600</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1656,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>46200</v>
+        <v>65600</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1664,16 +1706,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C35">
-        <v>45900</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>63100</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1685,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>45900</v>
+        <v>63100</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -1693,16 +1735,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="C36">
-        <v>45500</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1714,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>45500</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1722,13 +1764,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>43700</v>
+        <v>60900</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1743,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>43700</v>
+        <v>60900</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1751,13 +1793,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>58600</v>
       </c>
       <c r="D38">
-        <v>43500</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1772,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>43500</v>
+        <v>58600</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -1780,10 +1822,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C39">
-        <v>54600</v>
+        <v>71900</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1801,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>39600</v>
+        <v>56900</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -1809,10 +1851,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C40">
-        <v>39400</v>
+        <v>55500</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1830,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>39400</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -1838,16 +1880,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>39400</v>
+        <v>58500</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1859,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>39400</v>
+        <v>53700</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1867,13 +1909,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>39000</v>
+        <v>53300</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1888,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>39000</v>
+        <v>53300</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -1896,13 +1938,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="D43">
-        <v>37500</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1917,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>37500</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -1925,10 +1967,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C44">
-        <v>34900</v>
+        <v>50400</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1946,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>34900</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -1954,13 +1996,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C45">
-        <v>34400</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>49800</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1975,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>34400</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -1983,13 +2025,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C46">
-        <v>27300</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>20500</v>
+        <v>49700</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2004,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>32800</v>
+        <v>49700</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2012,10 +2054,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C47">
-        <v>32100</v>
+        <v>46200</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2033,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>32100</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2041,13 +2083,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>45900</v>
       </c>
       <c r="D48">
-        <v>31600</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2062,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>31600</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -2070,10 +2112,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C49">
-        <v>31500</v>
+        <v>45500</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2091,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>31500</v>
+        <v>45500</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -2099,13 +2141,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C50">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>43700</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2120,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>31200</v>
+        <v>43700</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2128,16 +2170,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="C51">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2149,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>30000</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2157,13 +2199,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C52">
-        <v>25500</v>
+        <v>71100</v>
       </c>
       <c r="D52">
-        <v>19400</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2178,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>29900</v>
+        <v>41100</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2186,10 +2228,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C53">
-        <v>29400</v>
+        <v>54600</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2207,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>29400</v>
+        <v>39600</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2215,10 +2257,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C54">
-        <v>27200</v>
+        <v>39400</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2236,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>27200</v>
+        <v>39400</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2244,13 +2286,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C55">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2265,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>25400</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -2273,13 +2315,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C56">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2294,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>24000</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2302,10 +2344,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C57">
-        <v>37700</v>
+        <v>34900</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2323,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>22700</v>
+        <v>34900</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -2331,13 +2373,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>27300</v>
       </c>
       <c r="D58">
-        <v>22600</v>
+        <v>20500</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2352,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>22600</v>
+        <v>32800</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2360,16 +2402,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C59">
-        <v>21600</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2381,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>21600</v>
+        <v>32700</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -2389,10 +2431,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C60">
-        <v>35400</v>
+        <v>32100</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2410,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>20400</v>
+        <v>32100</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -2418,10 +2460,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C61">
-        <v>33200</v>
+        <v>31500</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2439,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>18200</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -2447,10 +2489,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C62">
-        <v>16800</v>
+        <v>31200</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2468,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>16800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -2476,13 +2518,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="D63">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2497,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>15600</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
@@ -2505,13 +2547,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C64">
-        <v>29200</v>
+        <v>25500</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2526,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>14200</v>
+        <v>29900</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -2534,10 +2576,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C65">
-        <v>13100</v>
+        <v>29400</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2555,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>13100</v>
+        <v>29400</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
@@ -2563,13 +2605,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C66">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2584,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>8700</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
@@ -2592,13 +2634,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>27200</v>
       </c>
       <c r="D67">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2613,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>3900</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -2621,16 +2663,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="C68">
-        <v>18800</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>25900</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2642,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>3800</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
@@ -2650,28 +2692,434 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C69">
+        <v>25400</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>25400</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>64</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>39400</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>24400</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>70</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>22600</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>22600</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>43</v>
+      </c>
+      <c r="C72">
+        <v>21600</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73">
+        <v>35400</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>20400</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74">
+        <v>16800</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>72</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>15600</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76">
+        <v>13100</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77">
         <v>76</v>
       </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <v>3300</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>3300</v>
+      <c r="B77" t="s">
+        <v>69</v>
+      </c>
+      <c r="C77">
+        <v>24000</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>47</v>
+      </c>
+      <c r="C78">
+        <v>8700</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79">
+        <v>37700</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>22600</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>5200</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>73</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>3900</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>44</v>
+      </c>
+      <c r="C83">
+        <v>18800</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>3800</v>
       </c>
     </row>
   </sheetData>

--- a/public/res/leaderboards/Advanced.xlsx
+++ b/public/res/leaderboards/Advanced.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lawrence\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FAE6A3-C077-48C7-BB5F-62FF1E6BE251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102B6668-D514-4497-A342-533E62DAAD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{231F0BEC-F623-41AC-8721-73F4116A0546}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>#</t>
   </si>
@@ -312,6 +312,36 @@
   </si>
   <si>
     <t>Giorgio Atzarakis</t>
+  </si>
+  <si>
+    <t>Santiago Sassman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shanaa Srimanobhavan </t>
+  </si>
+  <si>
+    <t>Orville Wang</t>
+  </si>
+  <si>
+    <t>Leo Henschke</t>
+  </si>
+  <si>
+    <t>Alan LIu</t>
+  </si>
+  <si>
+    <t>Joseph Chen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minh Dam </t>
+  </si>
+  <si>
+    <t>James Barker</t>
+  </si>
+  <si>
+    <t>Alan Huynh</t>
+  </si>
+  <si>
+    <t>Sohom We</t>
   </si>
 </sst>
 </file>
@@ -712,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97B47B5-A6D7-41E5-A619-C36FE2241088}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -749,19 +779,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>54100</v>
+        <v>71000</v>
       </c>
       <c r="D2">
-        <v>139300</v>
+        <v>213600</v>
       </c>
       <c r="E2">
-        <v>185300</v>
+        <v>64800</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -770,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>363700</v>
+        <v>361600</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -778,16 +808,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>71000</v>
+        <v>54100</v>
       </c>
       <c r="D3">
-        <v>213600</v>
+        <v>139300</v>
       </c>
       <c r="E3">
-        <v>64800</v>
+        <v>185300</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -799,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>349400</v>
+        <v>348700</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -836,19 +866,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>118600</v>
+        <v>120000</v>
       </c>
       <c r="D5">
-        <v>123300</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>111500</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -857,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>226900</v>
+        <v>231500</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -865,16 +895,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>118600</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>123300</v>
       </c>
       <c r="E6">
-        <v>225800</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -886,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>225800</v>
+        <v>226900</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -894,19 +924,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="C7">
-        <v>65800</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>60900</v>
       </c>
       <c r="E7">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>174700</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -915,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>135800</v>
+        <v>220600</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -923,19 +953,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>29200</v>
+        <v>111300</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>117200</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>107400</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -944,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>131400</v>
+        <v>218700</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -952,16 +982,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="C9">
-        <v>146300</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>225800</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -973,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>131300</v>
+        <v>210800</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -981,19 +1011,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>45900</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>80700</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>123500</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>63600</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1002,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>126600</v>
+        <v>187100</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -1010,19 +1040,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>124800</v>
+        <v>3300</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>92700</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1031,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>124800</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1039,19 +1069,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>65600</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>123500</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100500</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1060,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>123500</v>
+        <v>166100</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1068,19 +1098,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C13">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>124800</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>28600</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1089,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>120000</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1097,19 +1127,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="C14">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>111100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>38700</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1118,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>118000</v>
+        <v>149800</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1126,19 +1156,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15">
-        <v>35500</v>
+        <v>34900</v>
       </c>
       <c r="D15">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1147,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>114700</v>
+        <v>147900</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1155,19 +1185,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C16">
-        <v>56200</v>
+        <v>45900</v>
       </c>
       <c r="D16">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>46000</v>
+        <v>74600</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>15900</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1176,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>113600</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1184,16 +1214,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C17">
-        <v>111300</v>
+        <v>65800</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1205,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>111300</v>
+        <v>135800</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1213,16 +1243,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>146300</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>111100</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1234,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>111100</v>
+        <v>131300</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1242,16 +1272,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>42000</v>
+        <v>58500</v>
       </c>
       <c r="E19">
-        <v>61500</v>
+        <v>102000</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1263,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>103500</v>
+        <v>130500</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1271,16 +1301,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>71900</v>
       </c>
       <c r="D20">
-        <v>94500</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>71300</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1292,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>94500</v>
+        <v>128200</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1300,16 +1330,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>45900</v>
       </c>
       <c r="D21">
-        <v>31600</v>
+        <v>80700</v>
       </c>
       <c r="E21">
-        <v>61500</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1321,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>93100</v>
+        <v>126600</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1329,19 +1359,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>18800</v>
       </c>
       <c r="D22">
-        <v>37500</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>54800</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>122300</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1350,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>92300</v>
+        <v>126100</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1358,19 +1388,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>31600</v>
       </c>
       <c r="E23">
-        <v>82700</v>
+        <v>61500</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>43100</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1379,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>82700</v>
+        <v>121200</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1387,16 +1417,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="D24">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>92700</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1408,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>81000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1416,16 +1446,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C25">
-        <v>33200</v>
+        <v>29200</v>
       </c>
       <c r="D25">
-        <v>62000</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>117200</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1437,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>80200</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1445,16 +1475,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C26">
-        <v>11400</v>
+        <v>35500</v>
       </c>
       <c r="D26">
-        <v>55000</v>
+        <v>79200</v>
       </c>
       <c r="E26">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1466,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>77400</v>
+        <v>114700</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1474,16 +1504,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>56200</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="E27">
-        <v>76500</v>
+        <v>46000</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1495,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>76500</v>
+        <v>113600</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1512,7 +1542,7 @@
         <v>31200</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>31600</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1524,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>76000</v>
+        <v>107600</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1532,16 +1562,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>88200</v>
+        <v>42000</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>61500</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1553,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>73200</v>
+        <v>103500</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1561,19 +1591,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>53300</v>
       </c>
       <c r="E30">
-        <v>72500</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>42800</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1582,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>72500</v>
+        <v>96100</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1590,13 +1620,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>84400</v>
+        <v>94500</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1611,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>69400</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1619,19 +1649,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>35500</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>81800</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>56500</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1640,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>66800</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1648,19 +1678,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>66400</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>88500</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1669,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>66400</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1677,16 +1707,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="C34">
-        <v>65600</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>82700</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1698,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>65600</v>
+        <v>82700</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1706,16 +1736,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>33200</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="E35">
-        <v>63100</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1727,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>63100</v>
+        <v>80200</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -1735,16 +1765,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="E36">
-        <v>63000</v>
+        <v>26000</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1756,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>63000</v>
+        <v>77400</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1764,16 +1794,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>60900</v>
+        <v>37500</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>54800</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1785,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>60900</v>
+        <v>77300</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1793,16 +1823,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="C38">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>76500</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1814,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>58600</v>
+        <v>76500</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -1822,19 +1852,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="C39">
-        <v>71900</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>43600</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1843,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>56900</v>
+        <v>76300</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -1851,13 +1881,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C40">
-        <v>55500</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>88200</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1872,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>55500</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -1880,16 +1910,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>58500</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>10200</v>
+        <v>72500</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1901,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>53700</v>
+        <v>72500</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1909,13 +1939,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>53300</v>
+        <v>84400</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1930,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>53300</v>
+        <v>69400</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -1938,16 +1968,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="C43">
-        <v>51000</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>81800</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1959,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>51000</v>
+        <v>66800</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -1967,13 +1997,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C44">
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>66400</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1988,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>50400</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -1996,16 +2026,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>49800</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2017,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>49800</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -2025,19 +2055,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="D46">
-        <v>49700</v>
+        <v>19400</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>30900</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2046,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>49700</v>
+        <v>60800</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2054,10 +2084,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C47">
-        <v>46200</v>
+        <v>58600</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2075,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>46200</v>
+        <v>58600</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2083,10 +2113,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="C48">
-        <v>45900</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2095,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>56100</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2104,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>45900</v>
+        <v>56100</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -2112,10 +2142,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="C49">
-        <v>45500</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2124,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>55600</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2133,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>45500</v>
+        <v>55600</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -2141,13 +2171,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>55500</v>
       </c>
       <c r="D50">
-        <v>43700</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2162,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>43700</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2170,7 +2200,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2179,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>42500</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2191,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>42500</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2199,10 +2229,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C52">
-        <v>71100</v>
+        <v>24000</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2211,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>42200</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2220,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>41100</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2228,10 +2258,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C53">
-        <v>54600</v>
+        <v>51000</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2249,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>39600</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2257,10 +2287,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C54">
-        <v>39400</v>
+        <v>50400</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2278,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>39400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2286,13 +2316,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>39000</v>
+        <v>49800</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2307,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>39000</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -2315,16 +2345,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>63100</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2336,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>37000</v>
+        <v>48100</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2344,10 +2374,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C57">
-        <v>34900</v>
+        <v>46200</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2365,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>34900</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -2373,19 +2403,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C58">
-        <v>27300</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>20500</v>
+        <v>43500</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>17400</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2394,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>32800</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2402,16 +2432,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>43700</v>
       </c>
       <c r="E59">
-        <v>32700</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2423,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>32700</v>
+        <v>43700</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -2431,16 +2461,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C60">
-        <v>32100</v>
+        <v>25400</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>17600</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2452,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>32100</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -2460,19 +2490,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C61">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>32600</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>22700</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -2481,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>31500</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -2489,10 +2519,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C62">
-        <v>31200</v>
+        <v>54600</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2510,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>31200</v>
+        <v>39600</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -2518,10 +2548,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C63">
-        <v>30000</v>
+        <v>39400</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2539,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>30000</v>
+        <v>39400</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
@@ -2547,19 +2577,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C64">
-        <v>25500</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>19400</v>
+        <v>0</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>37700</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -2568,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>29900</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -2576,13 +2606,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C65">
-        <v>29400</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2597,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>29400</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
@@ -2605,13 +2635,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>43500</v>
+        <v>49700</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2626,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>28500</v>
+        <v>34700</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
@@ -2634,10 +2664,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="C67">
-        <v>27200</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2646,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -2655,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>27200</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -2663,16 +2693,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>27300</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="E68">
-        <v>25900</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2684,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>25900</v>
+        <v>32800</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
@@ -2692,10 +2722,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C69">
-        <v>25400</v>
+        <v>32100</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2713,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>25400</v>
+        <v>32100</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
@@ -2721,13 +2751,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="D70">
-        <v>39400</v>
+        <v>0</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2742,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>24400</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
@@ -2750,13 +2780,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>31200</v>
       </c>
       <c r="D71">
-        <v>22600</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2771,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>22600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
@@ -2779,10 +2809,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C72">
-        <v>21600</v>
+        <v>45500</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2800,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>21600</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
@@ -2808,10 +2838,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C73">
-        <v>35400</v>
+        <v>30000</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2829,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>20400</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
@@ -2837,10 +2867,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C74">
-        <v>16800</v>
+        <v>29400</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2858,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>16800</v>
+        <v>29400</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
@@ -2866,19 +2896,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -2887,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>15600</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
@@ -2895,16 +2925,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="C76">
-        <v>13100</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2916,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>13100</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
@@ -2924,10 +2954,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C77">
-        <v>24000</v>
+        <v>27200</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2945,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>9000</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
@@ -2953,10 +2983,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="C78">
-        <v>8700</v>
+        <v>71100</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2974,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>8700</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
@@ -2982,16 +3012,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="C79">
-        <v>37700</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>25900</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3003,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>7700</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
@@ -3011,13 +3041,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>22600</v>
+        <v>39000</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3032,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>7600</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
@@ -3040,7 +3070,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3049,10 +3079,10 @@
         <v>0</v>
       </c>
       <c r="E81">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -3061,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>5200</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
@@ -3069,13 +3099,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>3900</v>
+        <v>22600</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3090,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>3900</v>
+        <v>22600</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
@@ -3098,10 +3128,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C83">
-        <v>18800</v>
+        <v>21600</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3119,7 +3149,297 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>3800</v>
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>33</v>
+      </c>
+      <c r="C84">
+        <v>35400</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>20400</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>100</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>17600</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>17600</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86">
+        <v>16800</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>72</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>15600</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>46</v>
+      </c>
+      <c r="C88">
+        <v>13100</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>64</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>39400</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>47</v>
+      </c>
+      <c r="C90">
+        <v>8700</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91">
+        <v>37700</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>89</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>22600</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>73</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>3900</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>3900</v>
       </c>
     </row>
   </sheetData>

--- a/public/res/leaderboards/Advanced.xlsx
+++ b/public/res/leaderboards/Advanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lawrence\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102B6668-D514-4497-A342-533E62DAAD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9001D001-B56F-4891-9C33-74465A6C19EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{231F0BEC-F623-41AC-8721-73F4116A0546}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>#</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Austen Wayne </t>
-  </si>
-  <si>
     <t>xavier hong</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
     <t>Marcus Miccelli</t>
   </si>
   <si>
-    <t xml:space="preserve">Rishi  Mahendranathan </t>
-  </si>
-  <si>
     <t>Mia Nguyen</t>
   </si>
   <si>
@@ -149,9 +143,6 @@
     <t>Arsalan Mishani</t>
   </si>
   <si>
-    <t xml:space="preserve">Pranay  Roberts </t>
-  </si>
-  <si>
     <t>Will Li</t>
   </si>
   <si>
@@ -161,9 +152,6 @@
     <t>Jingxuan Sun</t>
   </si>
   <si>
-    <t xml:space="preserve">Pranay Jai Kumar </t>
-  </si>
-  <si>
     <t>Aidan Poon</t>
   </si>
   <si>
@@ -176,9 +164,6 @@
     <t>Aahil Dalwai</t>
   </si>
   <si>
-    <t>Divyansh  Jain</t>
-  </si>
-  <si>
     <t>Austin Yam</t>
   </si>
   <si>
@@ -206,9 +191,6 @@
     <t>Ty Gredina</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyrus Han </t>
-  </si>
-  <si>
     <t>Ziggy Guan</t>
   </si>
   <si>
@@ -224,9 +206,6 @@
     <t>Jackie Xie</t>
   </si>
   <si>
-    <t xml:space="preserve">Jordan Rao </t>
-  </si>
-  <si>
     <t>Jason You</t>
   </si>
   <si>
@@ -248,9 +227,6 @@
     <t>Zichen Xue</t>
   </si>
   <si>
-    <t>Vojtech Zeman</t>
-  </si>
-  <si>
     <t>Zabrain Haider</t>
   </si>
   <si>
@@ -260,9 +236,6 @@
     <t>yi tang</t>
   </si>
   <si>
-    <t>kalabe araya</t>
-  </si>
-  <si>
     <t>kevin gonzalez arias</t>
   </si>
   <si>
@@ -284,18 +257,9 @@
     <t>Karwan</t>
   </si>
   <si>
-    <t>Yuquan  Hu</t>
-  </si>
-  <si>
     <t>Jazim Sodha</t>
   </si>
   <si>
-    <t xml:space="preserve">Sue Rhee </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derick </t>
-  </si>
-  <si>
     <t>Tiger Tam</t>
   </si>
   <si>
@@ -308,33 +272,21 @@
     <t>Keith Ng</t>
   </si>
   <si>
-    <t>Wilson Sha</t>
-  </si>
-  <si>
     <t>Giorgio Atzarakis</t>
   </si>
   <si>
     <t>Santiago Sassman</t>
   </si>
   <si>
-    <t xml:space="preserve">Shanaa Srimanobhavan </t>
-  </si>
-  <si>
     <t>Orville Wang</t>
   </si>
   <si>
     <t>Leo Henschke</t>
   </si>
   <si>
-    <t>Alan LIu</t>
-  </si>
-  <si>
     <t>Joseph Chen</t>
   </si>
   <si>
-    <t xml:space="preserve">Minh Dam </t>
-  </si>
-  <si>
     <t>James Barker</t>
   </si>
   <si>
@@ -342,13 +294,67 @@
   </si>
   <si>
     <t>Sohom We</t>
+  </si>
+  <si>
+    <t>Shanaa Srimanobhavan</t>
+  </si>
+  <si>
+    <t>Cyrus Han</t>
+  </si>
+  <si>
+    <t>Austin Huang</t>
+  </si>
+  <si>
+    <t>Austen Wayne</t>
+  </si>
+  <si>
+    <t>Jordan Rao</t>
+  </si>
+  <si>
+    <t>Yuquan Hu</t>
+  </si>
+  <si>
+    <t>Charmaine Qian Qian Tee</t>
+  </si>
+  <si>
+    <t>Sue Rhee</t>
+  </si>
+  <si>
+    <t>Vojtěch Zeman</t>
+  </si>
+  <si>
+    <t>Derick</t>
+  </si>
+  <si>
+    <t>Alan Liu</t>
+  </si>
+  <si>
+    <t>Minh Dam</t>
+  </si>
+  <si>
+    <t>Pranay Roberts</t>
+  </si>
+  <si>
+    <t>Pranay Jai Kumar</t>
+  </si>
+  <si>
+    <t>Divyansh Jain</t>
+  </si>
+  <si>
+    <t>akash jayaprabalan</t>
+  </si>
+  <si>
+    <t>Rishi Mahendranathan</t>
+  </si>
+  <si>
+    <t>Kalabe araya</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,20 +369,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -399,15 +391,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,35 +728,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97B47B5-A6D7-41E5-A619-C36FE2241088}">
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -779,28 +765,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>71000</v>
+        <v>54100</v>
       </c>
       <c r="D2">
-        <v>213600</v>
+        <v>139300</v>
       </c>
       <c r="E2">
-        <v>64800</v>
+        <v>185300</v>
       </c>
       <c r="F2">
-        <v>12200</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>361600</v>
+        <v>393700</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -808,19 +794,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>54100</v>
+        <v>71000</v>
       </c>
       <c r="D3">
-        <v>139300</v>
+        <v>213600</v>
       </c>
       <c r="E3">
-        <v>185300</v>
+        <v>64800</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -829,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>348700</v>
+        <v>361600</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -837,28 +823,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>34900</v>
       </c>
       <c r="D4">
-        <v>150700</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>130800</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>188000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>281500</v>
+        <v>335900</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -866,28 +852,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C5">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>150700</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>130800</v>
       </c>
       <c r="F5">
-        <v>111500</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>51800</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>231500</v>
+        <v>333300</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -895,28 +881,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="C6">
-        <v>118600</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>123300</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>123500</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>63600</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>128500</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>226900</v>
+        <v>315600</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -924,28 +910,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>65600</v>
       </c>
       <c r="D7">
-        <v>60900</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>174700</v>
+        <v>100500</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>145000</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>220600</v>
+        <v>311100</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -953,28 +939,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C8">
-        <v>111300</v>
+        <v>29200</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>117200</v>
       </c>
       <c r="F8">
-        <v>107400</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>163400</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>218700</v>
+        <v>279800</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -982,19 +968,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>225800</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>111500</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1003,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>210800</v>
+        <v>231500</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -1011,19 +997,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>118600</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>123300</v>
       </c>
       <c r="E10">
-        <v>123500</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>63600</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1032,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>187100</v>
+        <v>226900</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -1040,28 +1026,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>92700</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>94000</v>
+        <v>88500</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>137000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>175000</v>
+        <v>225500</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1069,19 +1055,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="C12">
-        <v>65600</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>60900</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>100500</v>
+        <v>174700</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1090,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>166100</v>
+        <v>220600</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1098,19 +1084,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>111300</v>
       </c>
       <c r="D13">
-        <v>124800</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>28600</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>17000</v>
+        <v>107400</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1119,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>155400</v>
+        <v>218700</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1127,7 +1113,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1142,13 +1128,13 @@
         <v>38700</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>62500</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>149800</v>
+        <v>212300</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1156,10 +1142,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C15">
-        <v>34900</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1168,16 +1154,16 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>204200</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>147900</v>
+        <v>204200</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1185,28 +1171,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C16">
-        <v>45900</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>53300</v>
       </c>
       <c r="E16">
-        <v>74600</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>15900</v>
+        <v>42800</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>103600</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>136400</v>
+        <v>199700</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1214,16 +1200,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="C17">
-        <v>65800</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>85000</v>
+        <v>225800</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1235,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>135800</v>
+        <v>195800</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1243,28 +1229,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="C18">
-        <v>146300</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>92700</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>131300</v>
+        <v>195700</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1272,28 +1258,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>59800</v>
       </c>
       <c r="D19">
-        <v>58500</v>
+        <v>31200</v>
       </c>
       <c r="E19">
-        <v>102000</v>
+        <v>31600</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>130500</v>
+        <v>193600</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1301,28 +1287,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C20">
-        <v>71900</v>
+        <v>25500</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="E20">
-        <v>71300</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>30900</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>126800</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>128200</v>
+        <v>172600</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1330,16 +1316,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>45900</v>
+        <v>58600</v>
       </c>
       <c r="D21">
-        <v>80700</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>107900</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1351,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>126600</v>
+        <v>166500</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1362,16 +1348,16 @@
         <v>44</v>
       </c>
       <c r="C22">
-        <v>18800</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>124800</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>28600</v>
       </c>
       <c r="F22">
-        <v>122300</v>
+        <v>17000</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1380,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>126100</v>
+        <v>140400</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1388,28 +1374,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>35500</v>
       </c>
       <c r="D23">
-        <v>31600</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>61500</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>43100</v>
+        <v>56500</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>44700</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>121200</v>
+        <v>136700</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1417,10 +1403,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="C24">
-        <v>118000</v>
+        <v>146300</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1438,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>118000</v>
+        <v>131300</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1446,16 +1432,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="C25">
-        <v>29200</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>58500</v>
       </c>
       <c r="E25">
-        <v>117200</v>
+        <v>102000</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1467,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>116400</v>
+        <v>130500</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1475,16 +1461,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C26">
-        <v>35500</v>
+        <v>71900</v>
       </c>
       <c r="D26">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>71300</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1496,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>114700</v>
+        <v>128200</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1504,28 +1490,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="C27">
-        <v>56200</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>46000</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>55600</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>70900</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>113600</v>
+        <v>126500</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1533,28 +1519,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="C28">
-        <v>59800</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>31600</v>
+        <v>32700</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>43600</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>46500</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>107600</v>
+        <v>122800</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1562,19 +1548,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>45900</v>
       </c>
       <c r="D29">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>61500</v>
+        <v>74600</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>15900</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1583,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>103500</v>
+        <v>121400</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1591,19 +1577,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>53300</v>
+        <v>31600</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>61500</v>
       </c>
       <c r="F30">
-        <v>42800</v>
+        <v>43100</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1612,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>96100</v>
+        <v>121200</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1620,16 +1606,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>65800</v>
       </c>
       <c r="D31">
-        <v>94500</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1641,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>94500</v>
+        <v>120800</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1649,10 +1635,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="C32">
-        <v>35500</v>
+        <v>118000</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1661,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>56500</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1670,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>92000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1678,19 +1664,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>56200</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="F33">
-        <v>88500</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1699,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>88500</v>
+        <v>113600</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1707,16 +1693,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>45900</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>80700</v>
       </c>
       <c r="E34">
-        <v>82700</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1728,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>82700</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1736,19 +1722,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="C35">
-        <v>33200</v>
+        <v>18800</v>
       </c>
       <c r="D35">
-        <v>62000</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>122300</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1757,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>80200</v>
+        <v>111100</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -1765,16 +1751,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C36">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>55000</v>
+        <v>42000</v>
       </c>
       <c r="E36">
-        <v>26000</v>
+        <v>61500</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1786,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>77400</v>
+        <v>103500</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1794,16 +1780,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>35500</v>
       </c>
       <c r="D37">
-        <v>37500</v>
+        <v>79200</v>
       </c>
       <c r="E37">
-        <v>54800</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1815,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>77300</v>
+        <v>99700</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1823,16 +1809,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>94500</v>
       </c>
       <c r="E38">
-        <v>76500</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1844,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>76500</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -1852,7 +1838,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1861,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>32700</v>
+        <v>82700</v>
       </c>
       <c r="F39">
-        <v>43600</v>
+        <v>0</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1873,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>76300</v>
+        <v>82700</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -1881,13 +1867,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>33200</v>
       </c>
       <c r="D40">
-        <v>88200</v>
+        <v>62000</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1902,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>73200</v>
+        <v>80200</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -1910,16 +1896,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="E41">
-        <v>72500</v>
+        <v>26000</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1931,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>72500</v>
+        <v>77400</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1939,16 +1925,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>84400</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>76500</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1960,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>69400</v>
+        <v>76500</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -1968,7 +1954,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1977,19 +1963,19 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>81800</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>73300</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>66800</v>
+        <v>73300</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -1997,13 +1983,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>66400</v>
+        <v>88200</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2018,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>66400</v>
+        <v>73200</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -2026,7 +2012,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2035,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>63000</v>
+        <v>72500</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2047,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>63000</v>
+        <v>72500</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -2055,19 +2041,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C46">
-        <v>25500</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>19400</v>
+        <v>84400</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>30900</v>
+        <v>0</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2076,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>60800</v>
+        <v>69400</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2084,16 +2070,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="C47">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>81800</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2105,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>58600</v>
+        <v>66800</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2113,7 +2099,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2122,10 +2108,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="F48">
-        <v>56100</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2134,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>56100</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -2142,10 +2128,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>55500</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2154,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>55600</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2163,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>55600</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -2171,13 +2157,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C50">
-        <v>55500</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>66400</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2192,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>55500</v>
+        <v>51400</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2200,10 +2186,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2212,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>52500</v>
+        <v>42200</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2221,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>52500</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2229,10 +2215,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="C52">
-        <v>24000</v>
+        <v>51000</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2241,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>42200</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2250,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>51200</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2261,7 +2247,7 @@
         <v>25</v>
       </c>
       <c r="C53">
-        <v>51000</v>
+        <v>50400</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2279,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>51000</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2287,13 +2273,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C54">
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>49800</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2308,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>50400</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2316,16 +2302,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>49800</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>63100</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2337,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>49800</v>
+        <v>48100</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -2345,16 +2331,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>37500</v>
       </c>
       <c r="E56">
-        <v>63100</v>
+        <v>54800</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2366,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>48100</v>
+        <v>47300</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2374,7 +2360,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C57">
         <v>46200</v>
@@ -2403,19 +2389,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>43500</v>
+        <v>43700</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>17400</v>
+        <v>0</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2424,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>45900</v>
+        <v>43700</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2432,16 +2418,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>25400</v>
       </c>
       <c r="D59">
-        <v>43700</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>17600</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2453,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>43700</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -2461,19 +2447,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C60">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>17600</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>56100</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2482,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>43000</v>
+        <v>41100</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -2490,7 +2476,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2519,7 +2505,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C62">
         <v>54600</v>
@@ -2548,7 +2534,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C63">
         <v>39400</v>
@@ -2577,7 +2563,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2589,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>37700</v>
+        <v>52500</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -2598,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>37700</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -2606,7 +2592,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2635,28 +2621,28 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>49700</v>
+        <v>0</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>37700</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>13300</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
       <c r="I66">
-        <v>34700</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
@@ -2664,19 +2650,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>49700</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
       <c r="F67">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -2685,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>33000</v>
+        <v>34700</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -2693,7 +2679,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C68">
         <v>27300</v>
@@ -2722,7 +2708,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C69">
         <v>32100</v>
@@ -2751,7 +2737,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C70">
         <v>31500</v>
@@ -2780,7 +2766,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>31200</v>
@@ -2809,19 +2795,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C72">
-        <v>45500</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>17400</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -2830,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>30500</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
@@ -2838,10 +2824,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C73">
-        <v>30000</v>
+        <v>45500</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2859,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>30000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
@@ -2867,10 +2853,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C74">
-        <v>29400</v>
+        <v>30000</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2888,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>29400</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
@@ -2896,19 +2882,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>29400</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>22300</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -2917,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>27500</v>
+        <v>29400</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
@@ -2925,7 +2911,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2934,10 +2920,10 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>42500</v>
+        <v>5200</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -2954,16 +2940,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C77">
-        <v>27200</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2975,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>27200</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
@@ -2983,10 +2969,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="C78">
-        <v>71100</v>
+        <v>27200</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3004,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>26100</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
@@ -3012,7 +2998,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3041,7 +3027,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3070,7 +3056,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3099,7 +3085,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3128,7 +3114,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C83">
         <v>21600</v>
@@ -3157,7 +3143,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C84">
         <v>35400</v>
@@ -3186,7 +3172,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -3195,10 +3181,10 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>17600</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -3207,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>17600</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
@@ -3215,16 +3201,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C86">
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>17600</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -3236,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>16800</v>
+        <v>17600</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
@@ -3244,13 +3230,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="D87">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3265,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>15600</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
@@ -3273,13 +3259,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C88">
-        <v>13100</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>15600</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3294,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>13100</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
@@ -3302,13 +3288,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>39400</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3317,13 +3303,13 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H89">
         <v>0</v>
       </c>
       <c r="I89">
-        <v>9400</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
@@ -3331,10 +3317,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C90">
-        <v>8700</v>
+        <v>13100</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3352,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>8700</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
@@ -3360,10 +3346,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C91">
-        <v>37700</v>
+        <v>71100</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3381,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>7700</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
@@ -3389,13 +3375,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>22600</v>
+        <v>39400</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3410,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>7600</v>
+        <v>9400</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
@@ -3418,27 +3404,85 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>101</v>
+      </c>
+      <c r="C94">
+        <v>37700</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>102</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
         <v>3900</v>
       </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93">
-        <v>0</v>
-      </c>
-      <c r="G93">
-        <v>0</v>
-      </c>
-      <c r="H93">
-        <v>0</v>
-      </c>
-      <c r="I93">
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
         <v>3900</v>
       </c>
     </row>
